--- a/artfynd/A 62117-2025 artfynd.xlsx
+++ b/artfynd/A 62117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131112846</v>
+        <v>131112856</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511159</v>
+        <v>511011</v>
       </c>
       <c r="R2" t="n">
-        <v>7037709</v>
+        <v>7037561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131112865</v>
+        <v>131112853</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,33 +811,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -851,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511019</v>
+        <v>511044</v>
       </c>
       <c r="R3" t="n">
-        <v>7037561</v>
+        <v>7037480</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,11 +876,6 @@
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på gran (&gt; 500 bålar).</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,17 +893,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,42 +926,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131112844</v>
+        <v>131112858</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510994</v>
+        <v>511126</v>
       </c>
       <c r="R4" t="n">
-        <v>7037511</v>
+        <v>7037660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt med bålar på gran (&gt; 500 bålar).</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,6 +1021,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1069,42 +1060,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131112845</v>
+        <v>131112859</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1112,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510982</v>
+        <v>511099</v>
       </c>
       <c r="R5" t="n">
-        <v>7037550</v>
+        <v>7037632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,7 +1146,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rikligt med bålar på gran (&gt; 500 bålar).</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,6 +1155,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1179,14 +1174,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,32 +1194,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131112854</v>
+        <v>131112860</v>
       </c>
       <c r="B6" t="n">
-        <v>80359</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1242,10 +1232,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511042</v>
+        <v>511032</v>
       </c>
       <c r="R6" t="n">
-        <v>7037501</v>
+        <v>7037541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,22 +1287,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,32 +1315,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131112853</v>
+        <v>131112861</v>
       </c>
       <c r="B7" t="n">
-        <v>80360</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1368,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511044</v>
+        <v>510933</v>
       </c>
       <c r="R7" t="n">
-        <v>7037480</v>
+        <v>7037435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,22 +1408,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1459,11 +1439,11 @@
         <v>131112864</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1590,14 +1570,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131112858</v>
+        <v>131112865</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1636,10 +1616,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511126</v>
+        <v>511019</v>
       </c>
       <c r="R9" t="n">
-        <v>7037660</v>
+        <v>7037561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1724,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131112859</v>
+        <v>131112842</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,33 +1715,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1770,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511099</v>
+        <v>511092</v>
       </c>
       <c r="R10" t="n">
-        <v>7037632</v>
+        <v>7037598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1806,11 +1778,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på gran (&gt; 500 bålar).</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1858,10 +1825,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131112860</v>
+        <v>131112843</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,21 +1836,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1896,10 +1863,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511032</v>
+        <v>510984</v>
       </c>
       <c r="R11" t="n">
-        <v>7037541</v>
+        <v>7037439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1979,10 +1946,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131112847</v>
+        <v>131112854</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1990,31 +1957,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2022,10 +1984,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511011</v>
+        <v>511042</v>
       </c>
       <c r="R12" t="n">
-        <v>7037468</v>
+        <v>7037501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2060,17 +2022,13 @@
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2081,17 +2039,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2109,10 +2072,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131112849</v>
+        <v>131112855</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,31 +2083,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2152,10 +2110,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510943</v>
+        <v>511045</v>
       </c>
       <c r="R13" t="n">
-        <v>7037434</v>
+        <v>7037478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2190,17 +2148,13 @@
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2211,17 +2165,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2239,37 +2198,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131112861</v>
+        <v>131112852</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2277,10 +2241,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510933</v>
+        <v>511154</v>
       </c>
       <c r="R14" t="n">
-        <v>7037435</v>
+        <v>7037711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2315,13 +2279,17 @@
           <t>2026-02-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rejäla äldre hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2340,9 +2308,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2360,10 +2333,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131112850</v>
+        <v>131112844</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2403,10 +2376,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510935</v>
+        <v>510994</v>
       </c>
       <c r="R15" t="n">
-        <v>7037434</v>
+        <v>7037511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2470,14 +2443,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2495,10 +2463,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131112851</v>
+        <v>131112845</v>
       </c>
       <c r="B16" t="n">
-        <v>58051</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2506,50 +2474,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Murukvisttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511030</v>
+        <v>510982</v>
       </c>
       <c r="R16" t="n">
-        <v>7037471</v>
+        <v>7037550</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2586,7 +2546,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Observation av 2 st födosökande talltitor som höll till på en grupp granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2601,6 +2561,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2618,10 +2598,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131112852</v>
+        <v>131112846</v>
       </c>
       <c r="B17" t="n">
-        <v>57889</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2629,16 +2609,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2661,10 +2641,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511154</v>
+        <v>511159</v>
       </c>
       <c r="R17" t="n">
-        <v>7037711</v>
+        <v>7037709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,7 +2681,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2728,14 +2708,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2753,10 +2728,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131112855</v>
+        <v>131112847</v>
       </c>
       <c r="B18" t="n">
-        <v>80359</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2764,26 +2739,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2791,10 +2771,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511045</v>
+        <v>511011</v>
       </c>
       <c r="R18" t="n">
-        <v>7037478</v>
+        <v>7037468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2829,13 +2809,17 @@
           <t>2026-02-10</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2846,22 +2830,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2879,10 +2858,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131112856</v>
+        <v>131112848</v>
       </c>
       <c r="B19" t="n">
-        <v>91818</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2890,28 +2869,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2921,10 +2901,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511011</v>
+        <v>510963</v>
       </c>
       <c r="R19" t="n">
-        <v>7037561</v>
+        <v>7037437</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2959,13 +2939,17 @@
           <t>2026-02-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3004,10 +2988,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131112842</v>
+        <v>131112849</v>
       </c>
       <c r="B20" t="n">
-        <v>83234</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,26 +2999,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3042,10 +3031,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511092</v>
+        <v>510943</v>
       </c>
       <c r="R20" t="n">
-        <v>7037598</v>
+        <v>7037434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3080,13 +3069,17 @@
           <t>2026-02-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3125,10 +3118,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131112843</v>
+        <v>131112850</v>
       </c>
       <c r="B21" t="n">
-        <v>83234</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,26 +3129,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3163,10 +3161,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510984</v>
+        <v>510935</v>
       </c>
       <c r="R21" t="n">
-        <v>7037439</v>
+        <v>7037434</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3201,13 +3199,17 @@
           <t>2026-02-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3226,9 +3228,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3246,10 +3253,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131112848</v>
+        <v>131112851</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,42 +3264,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Murukvisttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510963</v>
+        <v>511030</v>
       </c>
       <c r="R22" t="n">
-        <v>7037437</v>
+        <v>7037471</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3329,7 +3344,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Observation av 2 st födosökande talltitor som höll till på en grupp granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3344,21 +3359,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3373,127 +3373,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>131112857</v>
-      </c>
-      <c r="B23" t="n">
-        <v>91842</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Murukvisttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>511078</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7037578</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62117-2025 artfynd.xlsx
+++ b/artfynd/A 62117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112856</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -923,6 +933,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112853</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,6 +1072,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112858</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1191,6 +1211,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112859</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1312,6 +1337,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112860</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1433,6 +1463,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112861</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1567,6 +1602,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112864</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1701,6 +1741,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112865</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1822,6 +1867,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112842</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1943,6 +1993,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2069,6 +2124,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112854</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2195,6 +2255,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112855</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2330,6 +2395,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112852</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2460,6 +2530,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112844</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2595,6 +2670,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112845</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2725,6 +2805,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112846</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2855,6 +2940,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112847</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2985,6 +3075,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112848</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3115,6 +3210,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112849</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3250,6 +3350,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112850</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3373,8 +3478,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131112851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>